--- a/sheets/investing/bond-ladder-notes/bond-ladder-notes.xlsx
+++ b/sheets/investing/bond-ladder-notes/bond-ladder-notes.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBFDDEA8-3E95-4726-8349-28BC626A4A3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-35520" yWindow="2145" windowWidth="28800" windowHeight="15345" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="2070" windowWidth="28800" windowHeight="15345" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ladder Setup" sheetId="1" r:id="rId1"/>
